--- a/public/templates/attribution.xlsx
+++ b/public/templates/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -433,7 +435,84 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:J1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>权重基数*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>工具标签*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>归因说明</v>
+      </c>
+      <c r="G1" t="str">
+        <v>高分表现</v>
+      </c>
+      <c r="H1" t="str">
+        <v>典型诱因</v>
+      </c>
+      <c r="I1" t="str">
+        <v>建议动作</v>
+      </c>
+      <c r="J1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,7 +522,7 @@
         <v>所属模块*</v>
       </c>
       <c r="C1" t="str">
-        <v>依据量表编码*</v>
+        <v>依据量表编码</v>
       </c>
       <c r="D1" t="str">
         <v>优先级*</v>
@@ -458,50 +537,35 @@
         <v>等级中文名*</v>
       </c>
       <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
         <v>是否红线熔断*</v>
       </c>
-      <c r="I1" t="str">
-        <v>主归因*</v>
-      </c>
       <c r="J1" t="str">
-        <v>次归因</v>
+        <v>结果说明*</v>
       </c>
       <c r="K1" t="str">
-        <v>归因理由*</v>
+        <v>升级条件</v>
       </c>
       <c r="L1" t="str">
-        <v>工具标签*</v>
+        <v>升级目标</v>
       </c>
       <c r="M1" t="str">
-        <v>结果说明*</v>
+        <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J1"/>
   <sheetData>

--- a/public/templates/attribution.xlsx
+++ b/public/templates/attribution.xlsx
@@ -512,7 +512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -555,12 +555,18 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
